--- a/client/src/data/raw/mazo_07_higiene.xlsx
+++ b/client/src/data/raw/mazo_07_higiene.xlsx
@@ -888,13 +888,13 @@
         <v>Voy a ayudarle a girarse.</v>
       </c>
       <c r="N9" t="str">
-        <v>Please hold the support rail.</v>
+        <v>Por favor, sujete el riel de soporte.</v>
       </c>
       <c r="O9" t="str">
-        <v>I am going to change the sheets.</v>
+        <v>Voy a ayudarle a levantarse.</v>
       </c>
       <c r="P9" t="str">
-        <v>I am going to help you turn.</v>
+        <v>Voy a ayudarle a girarse.</v>
       </c>
       <c r="Q9" t="str">
         <v>hygiene</v>
